--- a/r4-ELGA-AustrianPatientSummary-40-27---apply-extensions-to-careplan/StructureDefinition-at-aps-careplan.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-40-27---apply-extensions-to-careplan/StructureDefinition-at-aps-careplan.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-10T07:10:15+00:00</t>
+    <t>2026-01-28T12:36:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -587,7 +587,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(CarePlan|4.0.1)
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-careplan)
 </t>
   </si>
   <si>
@@ -931,7 +931,7 @@
     <t>CarePlan.addresses</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Condition|4.0.1)
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-condition)
 </t>
   </si>
   <si>
@@ -1144,7 +1144,7 @@
     <t>CarePlan.activity.reference</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Appointment|4.0.1|CommunicationRequest|4.0.1|DeviceRequest|4.0.1|MedicationRequest|4.0.1|NutritionOrder|4.0.1|Task|4.0.1|ServiceRequest|4.0.1|VisionPrescription|4.0.1|RequestGroup|4.0.1)
+    <t xml:space="preserve">Reference(Appointment|CommunicationRequest|DeviceRequest|https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-medicationrequest|NutritionOrder|Task|ServiceRequest|VisionPrescription|RequestGroup)
 </t>
   </si>
   <si>
